--- a/data/trans_dic/P16A05-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A05-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,54</t>
+          <t>0,94; 4,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 10,14</t>
+          <t>3,75; 10,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,66</t>
+          <t>1,89; 6,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,16</t>
+          <t>1,4; 5,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 11,02</t>
+          <t>4,06; 10,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 12,39</t>
+          <t>5,57; 12,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 10,27</t>
+          <t>4,28; 10,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,53</t>
+          <t>2,5; 5,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,31</t>
+          <t>2,93; 6,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,93</t>
+          <t>5,16; 10,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,36</t>
+          <t>3,45; 7,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,83</t>
+          <t>2,32; 4,78</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,09</t>
+          <t>1,34; 3,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,42</t>
+          <t>2,03; 6,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,07</t>
+          <t>1,73; 4,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,23</t>
+          <t>4,14; 9,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 9,14</t>
+          <t>4,67; 9,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 11,26</t>
+          <t>6,1; 11,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,71</t>
+          <t>5,02; 9,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,9</t>
+          <t>7,69; 12,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,12</t>
+          <t>3,31; 6,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,92</t>
+          <t>4,67; 7,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,66</t>
+          <t>3,89; 6,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,52; 9,76</t>
+          <t>6,5; 9,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,74</t>
+          <t>0,68; 3,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,13</t>
+          <t>1,83; 6,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,52</t>
+          <t>1,57; 5,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,43</t>
+          <t>2,71; 7,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,65</t>
+          <t>1,2; 4,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,33</t>
+          <t>3,44; 8,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 10,03</t>
+          <t>5,77; 10,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,3</t>
+          <t>0,45; 2,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,98</t>
+          <t>1,71; 4,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,25</t>
+          <t>2,96; 6,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 8,22</t>
+          <t>4,77; 7,68</t>
         </is>
       </c>
     </row>
@@ -1142,57 +1142,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,95</t>
+          <t>0,88; 4,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,05</t>
+          <t>2,49; 6,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,34</t>
+          <t>1,15; 5,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,18</t>
+          <t>2,35; 6,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,59; 13,82</t>
+          <t>7,55; 13,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 11,8</t>
+          <t>5,7; 11,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,11</t>
+          <t>1,83; 5,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,04</t>
+          <t>1,6; 4,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,41</t>
+          <t>4,67; 8,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 8,65</t>
+          <t>4,78; 8,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,35</t>
+          <t>1,74; 4,32</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,08</t>
+          <t>0,86; 5,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,74</t>
+          <t>1,6; 7,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,85</t>
+          <t>2,3; 7,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,82</t>
+          <t>1,25; 5,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 9,46</t>
+          <t>3,09; 9,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,28; 21,58</t>
+          <t>11,08; 21,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,08; 18,92</t>
+          <t>8,84; 18,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,32; 13,18</t>
+          <t>8,26; 13,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,17</t>
+          <t>2,59; 6,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 13,2</t>
+          <t>7,33; 13,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 11,87</t>
+          <t>6,26; 11,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,5</t>
+          <t>5,58; 8,83</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,95</t>
+          <t>1,13; 5,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,44</t>
+          <t>1,43; 6,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,63</t>
+          <t>3,29; 7,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,9</t>
+          <t>1,63; 6,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,6</t>
+          <t>2,96; 9,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,49</t>
+          <t>3,13; 8,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,25; 13,63</t>
+          <t>8,43; 14,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,53</t>
+          <t>0,95; 3,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,38</t>
+          <t>2,62; 6,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,38</t>
+          <t>2,78; 6,67</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,39; 10,02</t>
+          <t>6,18; 9,82</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,3</t>
+          <t>1,56; 4,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,83</t>
+          <t>1,82; 4,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,45</t>
+          <t>2,2; 5,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,26</t>
+          <t>2,45; 5,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,94</t>
+          <t>3,47; 6,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,05</t>
+          <t>2,74; 5,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 9,62</t>
+          <t>5,4; 9,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,84</t>
+          <t>3,09; 10,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,04</t>
+          <t>2,89; 5,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 4,99</t>
+          <t>2,65; 4,91</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,27; 6,83</t>
+          <t>4,14; 6,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,03</t>
+          <t>3,6; 7,0</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,32</t>
+          <t>3,05; 6,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,16</t>
+          <t>1,67; 4,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,87</t>
+          <t>2,08; 4,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,81</t>
+          <t>1,83; 5,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,97</t>
+          <t>5,92; 9,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,42; 9,1</t>
+          <t>5,44; 9,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,5</t>
+          <t>6,52; 10,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,13; 13,83</t>
+          <t>9,21; 13,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,97; 7,41</t>
+          <t>4,93; 7,37</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,2</t>
+          <t>3,93; 6,23</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,25</t>
+          <t>4,71; 7,21</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,7</t>
+          <t>4,14; 8,85</t>
         </is>
       </c>
     </row>
@@ -1837,47 +1837,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,21</t>
+          <t>2,07; 3,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,02</t>
+          <t>2,76; 4,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,24</t>
+          <t>2,87; 4,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,21; 4,9</t>
+          <t>3,3; 4,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,14</t>
+          <t>4,6; 6,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,35; 8,0</t>
+          <t>6,22; 8,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,72; 8,55</t>
+          <t>6,78; 8,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,33; 8,89</t>
+          <t>6,57; 8,95</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,54; 4,54</t>
+          <t>3,5; 4,46</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,15</t>
+          <t>5,05; 6,18</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,29; 6,77</t>
+          <t>5,26; 6,74</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2637; 12407</t>
+          <t>2567; 12061</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10803; 29615</t>
+          <t>10952; 30145</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5429; 19554</t>
+          <t>5563; 18890</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4084; 16075</t>
+          <t>4361; 17124</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11350; 28737</t>
+          <t>10589; 27708</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15448; 34721</t>
+          <t>15608; 33946</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11880; 29636</t>
+          <t>12356; 31491</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7003; 16012</t>
+          <t>7242; 16394</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15373; 33702</t>
+          <t>15622; 34739</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30463; 56840</t>
+          <t>29541; 57384</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19396; 42896</t>
+          <t>20077; 41930</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13351; 29007</t>
+          <t>13948; 28740</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6781; 20188</t>
+          <t>6602; 19446</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9910; 32467</t>
+          <t>10265; 32476</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8608; 25491</t>
+          <t>8697; 25076</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21333; 47779</t>
+          <t>21415; 47593</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23385; 46083</t>
+          <t>23514; 46748</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31538; 58872</t>
+          <t>31897; 58551</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25985; 50768</t>
+          <t>26253; 50955</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39285; 61138</t>
+          <t>39509; 62469</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34237; 60985</t>
+          <t>32971; 60260</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47830; 81393</t>
+          <t>48001; 81161</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40091; 68286</t>
+          <t>39873; 69319</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67245; 100603</t>
+          <t>66993; 97912</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2117; 11939</t>
+          <t>2166; 12293</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6718; 23044</t>
+          <t>5917; 22372</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5119; 17586</t>
+          <t>5001; 18074</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8715; 23434</t>
+          <t>8549; 22183</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5356</t>
+          <t>0; 5391</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4054; 15846</t>
+          <t>4077; 15615</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11905; 27998</t>
+          <t>11557; 28066</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19598; 35017</t>
+          <t>20147; 35402</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3014; 15066</t>
+          <t>2941; 14240</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12239; 33103</t>
+          <t>11374; 32215</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19924; 40913</t>
+          <t>19356; 40866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33029; 54667</t>
+          <t>31720; 51080</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1057; 11554</t>
+          <t>1051; 11555</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3724; 18512</t>
+          <t>3289; 17708</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9360; 26085</t>
+          <t>9194; 25200</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2893; 16681</t>
+          <t>3604; 16418</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8531; 22966</t>
+          <t>8725; 22917</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29439; 53603</t>
+          <t>29308; 52739</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23252; 45683</t>
+          <t>22093; 45237</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8357; 24312</t>
+          <t>8689; 24095</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11955; 29463</t>
+          <t>11694; 29726</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36108; 64073</t>
+          <t>35568; 62049</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36499; 65520</t>
+          <t>36169; 63401</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15126; 34306</t>
+          <t>13728; 34012</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>983; 10332</t>
+          <t>1751; 10288</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4180; 16460</t>
+          <t>3394; 16438</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4615; 16586</t>
+          <t>4867; 16231</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2382; 8612</t>
+          <t>2241; 9029</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6636; 19645</t>
+          <t>6424; 20324</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24771; 47390</t>
+          <t>24335; 46909</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19841; 41348</t>
+          <t>19329; 40051</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17352; 27491</t>
+          <t>17230; 27828</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10261; 25367</t>
+          <t>10631; 26077</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31852; 57030</t>
+          <t>31698; 57524</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27709; 51038</t>
+          <t>26924; 50881</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20700; 32941</t>
+          <t>21608; 34209</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6524</t>
+          <t>0; 6473</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2988; 13570</t>
+          <t>3085; 13971</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3713; 16950</t>
+          <t>3763; 16522</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8702; 20581</t>
+          <t>8871; 21183</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4105; 16408</t>
+          <t>4540; 17310</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8161; 24014</t>
+          <t>8274; 25400</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7962; 23195</t>
+          <t>8558; 23046</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21204; 35030</t>
+          <t>21665; 36127</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5991; 19367</t>
+          <t>5235; 19348</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14418; 35271</t>
+          <t>14514; 33435</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14601; 34226</t>
+          <t>14887; 35742</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>33643; 52797</t>
+          <t>32563; 51710</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9283; 26475</t>
+          <t>9617; 25659</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12314; 31988</t>
+          <t>12030; 31722</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15080; 35761</t>
+          <t>14468; 34660</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15576; 32820</t>
+          <t>15308; 33507</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22136; 44284</t>
+          <t>22172; 43123</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19620; 41986</t>
+          <t>18982; 40722</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36309; 66501</t>
+          <t>37324; 67884</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>30075; 83493</t>
+          <t>26207; 84891</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36566; 63152</t>
+          <t>36185; 63671</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36290; 67751</t>
+          <t>35988; 66621</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>57612; 92020</t>
+          <t>55846; 90454</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>52060; 103583</t>
+          <t>53064; 103064</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>23699; 46959</t>
+          <t>22657; 46293</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12673; 32350</t>
+          <t>12952; 34167</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16390; 37905</t>
+          <t>16164; 36158</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14272; 53994</t>
+          <t>16971; 54901</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>47608; 78095</t>
+          <t>46405; 75699</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>44560; 74868</t>
+          <t>44793; 75818</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>53098; 86787</t>
+          <t>53885; 87804</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>65234; 98884</t>
+          <t>65829; 97647</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>75831; 113118</t>
+          <t>75185; 112448</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>62792; 99149</t>
+          <t>62880; 99712</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>74933; 116265</t>
+          <t>75592; 115638</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>72953; 143048</t>
+          <t>68105; 145481</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>68210; 105061</t>
+          <t>67807; 103312</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>92671; 137543</t>
+          <t>94380; 141186</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100365; 144005</t>
+          <t>97572; 140507</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>111138; 169391</t>
+          <t>114257; 169604</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>155861; 207406</t>
+          <t>155481; 207452</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>225291; 283634</t>
+          <t>220617; 285627</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>238343; 303133</t>
+          <t>240366; 304472</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>231360; 325044</t>
+          <t>240418; 327373</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>235596; 301929</t>
+          <t>233080; 297133</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>329798; 410502</t>
+          <t>329289; 410329</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>348475; 426976</t>
+          <t>350080; 429092</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>376179; 481945</t>
+          <t>373970; 479385</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A05-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A05-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,42</t>
+          <t>0,95; 4,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 10,32</t>
+          <t>3,71; 9,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,43</t>
+          <t>1,75; 6,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,5</t>
+          <t>1,21; 4,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 10,62</t>
+          <t>4,03; 10,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 12,11</t>
+          <t>5,4; 12,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,91</t>
+          <t>4,19; 10,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,66</t>
+          <t>2,47; 5,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,51</t>
+          <t>3,1; 6,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 10,02</t>
+          <t>5,45; 10,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 7,2</t>
+          <t>3,43; 7,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,78</t>
+          <t>2,21; 4,51</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,94</t>
+          <t>1,27; 4,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,42</t>
+          <t>2,01; 6,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,99</t>
+          <t>1,88; 5,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 9,2</t>
+          <t>4,17; 8,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 9,28</t>
+          <t>4,6; 8,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 11,2</t>
+          <t>5,96; 11,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,74</t>
+          <t>5,06; 9,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,16</t>
+          <t>7,61; 11,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,04</t>
+          <t>3,43; 5,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,89</t>
+          <t>4,67; 7,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 6,76</t>
+          <t>4,02; 6,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 9,5</t>
+          <t>6,39; 9,57</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,86</t>
+          <t>0,91; 3,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,92</t>
+          <t>1,85; 6,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,67</t>
+          <t>1,48; 5,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,03</t>
+          <t>2,72; 7,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,58</t>
+          <t>1,18; 4,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,35</t>
+          <t>3,68; 8,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 10,14</t>
+          <t>5,65; 10,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,18</t>
+          <t>0,45; 2,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,85</t>
+          <t>1,86; 4,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,24</t>
+          <t>3,08; 6,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 7,68</t>
+          <t>4,91; 7,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,22</t>
+          <t>0,3; 3,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,73</t>
+          <t>1,1; 4,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,81</t>
+          <t>2,48; 6,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,25</t>
+          <t>0,97; 5,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,17</t>
+          <t>2,25; 6,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,55; 13,59</t>
+          <t>7,67; 13,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 11,68</t>
+          <t>5,79; 11,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,07</t>
+          <t>2,66; 5,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,07</t>
+          <t>1,57; 4,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,14</t>
+          <t>4,68; 8,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 8,37</t>
+          <t>4,82; 8,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,32</t>
+          <t>2,09; 4,54</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,06</t>
+          <t>0,87; 4,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 7,73</t>
+          <t>1,91; 7,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,68</t>
+          <t>2,27; 8,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,05</t>
+          <t>1,15; 5,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,79</t>
+          <t>3,21; 9,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,08; 21,36</t>
+          <t>11,14; 21,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 18,32</t>
+          <t>9,21; 18,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,26; 13,34</t>
+          <t>7,82; 12,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,35</t>
+          <t>2,43; 6,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,33; 13,31</t>
+          <t>7,34; 12,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,26; 11,84</t>
+          <t>6,2; 11,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,58; 8,83</t>
+          <t>4,93; 8,19</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,1</t>
+          <t>1,09; 5,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,28</t>
+          <t>1,47; 6,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,29; 7,86</t>
+          <t>3,19; 7,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,22</t>
+          <t>1,53; 5,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,1</t>
+          <t>3,14; 8,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,13; 8,44</t>
+          <t>2,97; 8,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,43; 14,05</t>
+          <t>8,33; 13,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,52</t>
+          <t>1,11; 3,54</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,04</t>
+          <t>2,54; 6,12</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,67</t>
+          <t>2,83; 6,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,18; 9,82</t>
+          <t>6,31; 9,58</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,17</t>
+          <t>1,53; 4,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,79</t>
+          <t>1,91; 4,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,28</t>
+          <t>2,22; 5,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,37</t>
+          <t>2,59; 5,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,76</t>
+          <t>3,56; 7,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,87</t>
+          <t>2,76; 5,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,82</t>
+          <t>5,46; 9,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 10,0</t>
+          <t>7,34; 11,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,08</t>
+          <t>2,8; 4,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,91</t>
+          <t>2,58; 4,68</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 6,71</t>
+          <t>4,17; 6,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 7,0</t>
+          <t>5,45; 7,84</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,23</t>
+          <t>3,09; 6,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,4</t>
+          <t>1,51; 4,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,64</t>
+          <t>2,12; 4,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,91</t>
+          <t>3,81; 6,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,92; 9,66</t>
+          <t>5,73; 9,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,44; 9,22</t>
+          <t>5,32; 8,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,52; 10,63</t>
+          <t>6,52; 10,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,66</t>
+          <t>8,65; 12,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,37</t>
+          <t>4,93; 7,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,23</t>
+          <t>3,99; 6,25</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,71; 7,21</t>
+          <t>4,72; 7,3</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,14; 8,85</t>
+          <t>6,71; 8,96</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -1837,32 +1837,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,15</t>
+          <t>2,11; 3,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,13</t>
+          <t>2,66; 4,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,14</t>
+          <t>2,94; 4,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,3; 4,9</t>
+          <t>3,65; 5,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,14</t>
+          <t>4,53; 6,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,05</t>
+          <t>6,26; 8,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1872,27 +1872,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,57; 8,95</t>
+          <t>7,74; 9,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,46</t>
+          <t>3,49; 4,43</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,73; 5,89</t>
+          <t>4,75; 5,93</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,18</t>
+          <t>5,0; 6,15</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,74</t>
+          <t>5,89; 6,9</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>20086</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2567; 12061</t>
+          <t>2581; 12199</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10952; 30145</t>
+          <t>10844; 28749</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5563; 18890</t>
+          <t>5149; 18261</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4361; 17124</t>
+          <t>3872; 14849</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10589; 27708</t>
+          <t>10501; 26701</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15608; 33946</t>
+          <t>15141; 35711</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12356; 31491</t>
+          <t>12104; 29912</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7242; 16394</t>
+          <t>7820; 17421</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15622; 34739</t>
+          <t>16528; 36598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29541; 57384</t>
+          <t>31207; 58565</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20077; 41930</t>
+          <t>20007; 41978</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13948; 28740</t>
+          <t>14023; 28605</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32024</t>
+          <t>32424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50447</t>
+          <t>52005</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82471</t>
+          <t>84429</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6602; 19446</t>
+          <t>6287; 20308</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10265; 32476</t>
+          <t>10173; 32315</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8697; 25076</t>
+          <t>9451; 25643</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21415; 47593</t>
+          <t>22062; 47471</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23514; 46748</t>
+          <t>23168; 45278</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31897; 58551</t>
+          <t>31159; 58566</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26253; 50955</t>
+          <t>26465; 49712</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39509; 62469</t>
+          <t>41518; 63624</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32971; 60260</t>
+          <t>34192; 59736</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48001; 81161</t>
+          <t>48054; 81431</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39873; 69319</t>
+          <t>41213; 69552</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>66993; 97912</t>
+          <t>68735; 102875</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>14177</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26887</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41387</t>
+          <t>41304</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2166; 12293</t>
+          <t>2896; 12428</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5917; 22372</t>
+          <t>5981; 22296</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5001; 18074</t>
+          <t>4707; 17992</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8549; 22183</t>
+          <t>8590; 22228</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5391</t>
+          <t>0; 5244</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4077; 15615</t>
+          <t>4031; 15487</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11557; 28066</t>
+          <t>12371; 28475</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20147; 35402</t>
+          <t>20139; 36074</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2941; 14240</t>
+          <t>2936; 13086</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11374; 32215</t>
+          <t>12372; 32065</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19356; 40866</t>
+          <t>20146; 40411</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31720; 51080</t>
+          <t>33018; 53058</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>24751</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1051; 11555</t>
+          <t>1063; 12089</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3289; 17708</t>
+          <t>4125; 18271</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9194; 25200</t>
+          <t>9180; 25247</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3604; 16418</t>
+          <t>3608; 19588</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8725; 22917</t>
+          <t>8351; 22967</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29308; 52739</t>
+          <t>29740; 53785</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22093; 45237</t>
+          <t>22418; 44961</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8689; 24095</t>
+          <t>11224; 24945</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11694; 29726</t>
+          <t>11441; 29692</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35568; 62049</t>
+          <t>35677; 64760</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36169; 63401</t>
+          <t>36491; 64577</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13728; 34012</t>
+          <t>16620; 36045</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21874</t>
+          <t>22923</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26665</t>
+          <t>27969</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1751; 10288</t>
+          <t>1764; 9440</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3394; 16438</t>
+          <t>4071; 16395</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4867; 16231</t>
+          <t>4793; 17313</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2241; 9029</t>
+          <t>2369; 10410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6424; 20324</t>
+          <t>6662; 20715</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24335; 46909</t>
+          <t>24459; 46893</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19329; 40051</t>
+          <t>20121; 40089</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17230; 27828</t>
+          <t>17759; 28835</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10631; 26077</t>
+          <t>9986; 26267</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31698; 57524</t>
+          <t>31710; 55522</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26924; 50881</t>
+          <t>26661; 49888</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21608; 34209</t>
+          <t>21324; 35457</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>27784</t>
+          <t>28214</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>41732</t>
+          <t>41837</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6473</t>
+          <t>0; 6681</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3085; 13971</t>
+          <t>2999; 14461</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3763; 16522</t>
+          <t>3877; 16528</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8871; 21183</t>
+          <t>8629; 21186</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4540; 17310</t>
+          <t>4249; 16365</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8274; 25400</t>
+          <t>8770; 24105</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8558; 23046</t>
+          <t>8112; 22752</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21665; 36127</t>
+          <t>21963; 36130</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5235; 19348</t>
+          <t>6068; 19432</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14514; 33435</t>
+          <t>14059; 33825</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14887; 35742</t>
+          <t>15167; 35149</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>32563; 51710</t>
+          <t>33727; 51223</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23384</t>
+          <t>27424</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>59236</t>
+          <t>70380</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>82621</t>
+          <t>97804</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9617; 25659</t>
+          <t>9404; 26010</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12030; 31722</t>
+          <t>12672; 31661</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14468; 34660</t>
+          <t>14571; 33123</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15308; 33507</t>
+          <t>18619; 39654</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22172; 43123</t>
+          <t>22705; 45426</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18982; 40722</t>
+          <t>19178; 40048</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37324; 67884</t>
+          <t>37733; 66536</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>26207; 84891</t>
+          <t>56635; 85807</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36185; 63671</t>
+          <t>35057; 62032</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>35988; 66621</t>
+          <t>34974; 63553</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55846; 90454</t>
+          <t>56191; 91676</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>53064; 103064</t>
+          <t>81211; 116931</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36466</t>
+          <t>41093</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>78643</t>
+          <t>85254</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>115110</t>
+          <t>126347</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22657; 46293</t>
+          <t>22974; 46236</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12952; 34167</t>
+          <t>11741; 33660</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16164; 36158</t>
+          <t>16496; 37146</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16971; 54901</t>
+          <t>30427; 54269</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>46405; 75699</t>
+          <t>44881; 78022</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>44793; 75818</t>
+          <t>43781; 73938</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>53885; 87804</t>
+          <t>53893; 87488</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>65829; 97647</t>
+          <t>71791; 99657</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>75185; 112448</t>
+          <t>75214; 113860</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>62880; 99712</t>
+          <t>63903; 99910</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>75592; 115638</t>
+          <t>75819; 117190</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>68105; 145481</t>
+          <t>109299; 145834</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>141714</t>
+          <t>150440</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>290887</t>
+          <t>314087</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>432601</t>
+          <t>464527</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>67807; 103312</t>
+          <t>69233; 104896</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>94380; 141186</t>
+          <t>91134; 138415</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97572; 140507</t>
+          <t>99860; 142104</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>114257; 169604</t>
+          <t>128724; 176451</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>155481; 207452</t>
+          <t>153029; 205573</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>220617; 285627</t>
+          <t>222140; 287276</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>240366; 304472</t>
+          <t>240175; 304450</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>240418; 327373</t>
+          <t>288698; 344031</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>233080; 297133</t>
+          <t>232017; 294823</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>329289; 410329</t>
+          <t>330772; 412982</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>350080; 429092</t>
+          <t>347022; 426620</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>373970; 479385</t>
+          <t>428107; 501395</t>
         </is>
       </c>
     </row>
